--- a/OMOP Analysis/Results/Yearly/yearly_combined_bootstrap_summary_encounters_OMOP.xlsx
+++ b/OMOP Analysis/Results/Yearly/yearly_combined_bootstrap_summary_encounters_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -499,241 +499,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>14.85</v>
+        <v>26.416</v>
       </c>
       <c r="D4">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="E4">
-        <v>0.099</v>
+        <v>0.15</v>
       </c>
       <c r="F4">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="G4">
-        <v>14.659</v>
+        <v>26.11</v>
       </c>
       <c r="H4">
-        <v>15.049</v>
+        <v>26.699</v>
       </c>
       <c r="I4">
-        <v>14.656</v>
+        <v>26.121</v>
       </c>
       <c r="J4">
-        <v>15.046</v>
+        <v>26.717</v>
       </c>
       <c r="K4">
-        <v>14.658</v>
+        <v>26.104</v>
       </c>
       <c r="L4">
-        <v>15.049</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>12.616</v>
+        <v>20.352</v>
       </c>
       <c r="D5">
-        <v>0.013</v>
+        <v>0.032</v>
       </c>
       <c r="E5">
-        <v>0.115</v>
+        <v>0.18</v>
       </c>
       <c r="F5">
-        <v>0.004</v>
+        <v>0.006</v>
       </c>
       <c r="G5">
-        <v>12.396</v>
+        <v>19.991</v>
       </c>
       <c r="H5">
-        <v>12.846</v>
+        <v>20.697</v>
       </c>
       <c r="I5">
-        <v>12.397</v>
+        <v>20.01</v>
       </c>
       <c r="J5">
-        <v>12.84</v>
+        <v>20.72</v>
       </c>
       <c r="K5">
-        <v>12.397</v>
+        <v>19.975</v>
       </c>
       <c r="L5">
-        <v>12.841</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>26.487</v>
-      </c>
-      <c r="D6">
-        <v>0.02</v>
-      </c>
-      <c r="E6">
-        <v>0.142</v>
-      </c>
-      <c r="F6">
-        <v>0.004</v>
-      </c>
-      <c r="G6">
-        <v>26.208</v>
-      </c>
-      <c r="H6">
-        <v>26.764</v>
-      </c>
-      <c r="I6">
-        <v>26.2</v>
-      </c>
-      <c r="J6">
-        <v>26.752</v>
-      </c>
-      <c r="K6">
-        <v>26.222</v>
-      </c>
-      <c r="L6">
-        <v>26.774</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>20.362</v>
-      </c>
-      <c r="D7">
-        <v>0.03</v>
-      </c>
-      <c r="E7">
-        <v>0.173</v>
-      </c>
-      <c r="F7">
-        <v>0.005</v>
-      </c>
-      <c r="G7">
-        <v>20.039</v>
-      </c>
-      <c r="H7">
-        <v>20.718</v>
-      </c>
-      <c r="I7">
-        <v>20.042</v>
-      </c>
-      <c r="J7">
-        <v>20.714</v>
-      </c>
-      <c r="K7">
-        <v>20.026</v>
-      </c>
-      <c r="L7">
-        <v>20.699</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>15.308</v>
-      </c>
-      <c r="D8">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="E8">
-        <v>0.097</v>
-      </c>
-      <c r="F8">
-        <v>0.003</v>
-      </c>
-      <c r="G8">
-        <v>15.117</v>
-      </c>
-      <c r="H8">
-        <v>15.498</v>
-      </c>
-      <c r="I8">
-        <v>15.119</v>
-      </c>
-      <c r="J8">
-        <v>15.486</v>
-      </c>
-      <c r="K8">
-        <v>15.13</v>
-      </c>
-      <c r="L8">
-        <v>15.497</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>12.728</v>
-      </c>
-      <c r="D9">
-        <v>0.013</v>
-      </c>
-      <c r="E9">
-        <v>0.115</v>
-      </c>
-      <c r="F9">
-        <v>0.004</v>
-      </c>
-      <c r="G9">
-        <v>12.511</v>
-      </c>
-      <c r="H9">
-        <v>12.963</v>
-      </c>
-      <c r="I9">
-        <v>12.512</v>
-      </c>
-      <c r="J9">
-        <v>12.961</v>
-      </c>
-      <c r="K9">
-        <v>12.504</v>
-      </c>
-      <c r="L9">
-        <v>12.953</v>
+        <v>20.686</v>
       </c>
     </row>
   </sheetData>
